--- a/rules/CORE-000473/negative/02/data/unit-test-coreid-CG0272-negative 2.xlsx
+++ b/rules/CORE-000473/negative/02/data/unit-test-coreid-CG0272-negative 2.xlsx
@@ -523,7 +523,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -546,48 +546,68 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="str">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="str">
         <v>ts.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="4" t="str">
         <v>TSPARMCD</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="F2" s="4" t="str">
         <v>TDIGRP</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="str">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="str">
         <v>ts.xpt</v>
       </c>
-      <c r="C3" s="2" t="str">
+      <c r="C3" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="str">
+      <c r="E3" s="4" t="str">
         <v>TSVAL</v>
       </c>
-      <c r="F3" s="2" t="str">
+      <c r="F3" s="4" t="str">
         <v>Patients with Probable Mild to Moderate Alzheimers Disease</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>ts.xpt</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D4" s="2">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <v>TSGRPID</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -851,7 +871,7 @@
       <c r="C8" s="4">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="7" t="str">
         <v>1</v>
       </c>
       <c r="E8" s="7" t="str">
@@ -913,25 +933,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="str">
+      <c r="A10" s="4" t="str">
         <v>CDISCPILOT02</v>
       </c>
-      <c r="B10" s="2" t="str">
+      <c r="B10" s="4" t="str">
         <v>TS</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>3</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="4">
         <v>2</v>
       </c>
-      <c r="E10" s="2" t="str">
+      <c r="E10" s="4" t="str">
         <v>TDIGRP</v>
       </c>
-      <c r="F10" s="2" t="str">
+      <c r="F10" s="4" t="str">
         <v>Diagnosis Group</v>
       </c>
-      <c r="G10" s="2" t="str">
+      <c r="G10" s="4" t="str">
         <v>HEALTHY SUBJECTS</v>
       </c>
     </row>
